--- a/client/public/templates/PriceRight_Intermediates_Import_Template.xlsx
+++ b/client/public/templates/PriceRight_Intermediates_Import_Template.xlsx
@@ -398,14 +398,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A70"/>
   <cols>
     <col min="1" max="1" width="100.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Intermediate Materials Import Template</v>
+        <v>PriceRight — Intermediate Materials Import Template</v>
       </c>
     </row>
     <row r="2">
@@ -415,75 +415,365 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Fill in your data on the Import Data sheet.</v>
+        <v>HOW TO USE THIS TEMPLATE</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>One row per component material. Repeat Intermediate Name, Category, Unit, Overhead %, Yield %, Margin %, and Bulk Quantity on every row for the same intermediate.</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>STEPS:</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Component Name must match a raw material already in PriceRight.</v>
+        <v>1. Click the "Import Data" tab at the bottom of this file</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Leave Component Name blank for intermediates with no components yet.</v>
+        <v>2. Review the sample rows to understand the expected format</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>3. Delete the sample data rows (rows 2 and below)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Overhead %: factory overhead added to material cost (e.g. 10 = 10%). Default 0.</v>
+        <v xml:space="preserve">   — Keep row 1 (the column headers) — do not delete or edit it</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Yield %: usable output from the batch (e.g. 85 = 85%). Default 100.</v>
+        <v>4. Enter your real data starting from row 2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Margin %: profit margin on cost (e.g. 20 = 20%). Default 0.</v>
+        <v>5. Save the file (keep the .xlsx format)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Bulk Quantity: units produced per batch. Default 1.</v>
+        <v>6. In PriceRight go to Materials → Intermediate tab → More → Import</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v xml:space="preserve">   and select this file</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>NOTE: Each intermediate material can have multiple components.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Add one row per component. Repeat the Intermediate Name,</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Category, Unit and settings on each row for the same material.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>IMPORTANT NOTES:</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>— Do not rename or delete any column headers</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>— Do not add extra columns</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>— Leave optional fields blank if not needed</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>— Currency codes must match currencies set up in PriceRight</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>COLUMN GUIDE:</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v xml:space="preserve">  Intermediate Name — Required</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve">    Name of the intermediate (semi-processed) material</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v xml:space="preserve">    Example: Refined Peanut Paste</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v xml:space="preserve">  Category — Required</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">    Material category</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v xml:space="preserve">    Example: Processed</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v xml:space="preserve">  Unit — Required</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v xml:space="preserve">    Unit of the finished intermediate material</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v xml:space="preserve">    Example: Kg</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v xml:space="preserve">  Overhead % — Optional (default: 0)</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v xml:space="preserve">    Overhead cost as a percentage of material cost</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v xml:space="preserve">    Example: 10  (means 10% overhead added to batch cost)</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v xml:space="preserve">  Yield % — Optional (default: 100)</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v xml:space="preserve">    Expected output as a percentage of input</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v xml:space="preserve">    Example: 85  (means 15% loss during processing)</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v xml:space="preserve">  Margin % — Optional (default: 0)</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v xml:space="preserve">    Profit margin percentage to add to cost per unit</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v xml:space="preserve">    Example: 0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v xml:space="preserve">  Bulk Quantity — Optional (default: 1)</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v xml:space="preserve">    The batch output quantity this recipe produces</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v xml:space="preserve">    Example: 20  (this recipe produces 20 Kg per batch)</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v xml:space="preserve">  Component Name — Required</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v xml:space="preserve">    Name of a raw material used in this batch</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v xml:space="preserve">    Must already exist in PriceRight as a primary material</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v xml:space="preserve">    Example: Raw Peanuts</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v xml:space="preserve">  Component Quantity — Required</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v xml:space="preserve">    Quantity of this component used per batch</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v xml:space="preserve">    Example: 25  (25 Kg of Raw Peanuts per batch)</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v xml:space="preserve">  Notes — Optional</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v xml:space="preserve">    Any additional notes</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v xml:space="preserve">    Example: Yield-based processing</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>SAMPLE DATA:</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>The Import Data sheet contains sample rows showing the correct format.</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Delete them before importing.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A70"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J5"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="14.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="1" max="1" width="21.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="22.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -515,12 +805,140 @@
         <v>Component Quantity</v>
       </c>
       <c r="J1" t="str">
-        <v>Component Unit</v>
+        <v>Notes</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Refined Peanut Paste</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Processed</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Kg</v>
+      </c>
+      <c r="D2">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>85</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>20</v>
+      </c>
+      <c r="H2" t="str">
+        <v>Raw Peanuts</v>
+      </c>
+      <c r="I2">
+        <v>25</v>
+      </c>
+      <c r="J2" t="str">
+        <v>First component — main ingredient</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Refined Peanut Paste</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Processed</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Kg</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>85</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>20</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Salt (Iodised)</v>
+      </c>
+      <c r="I3">
+        <v>0.5</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Second component — same intermediate</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Blended Pepper Mix</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Processed Seasonings</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Kg</v>
+      </c>
+      <c r="D4">
+        <v>12</v>
+      </c>
+      <c r="E4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>10</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Pepper (Ground Chilli)</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Third row — different intermediate</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Blended Pepper Mix</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Processed Seasonings</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Kg</v>
+      </c>
+      <c r="D5">
+        <v>12</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Garlic Powder</v>
+      </c>
+      <c r="I5">
+        <v>1.5</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Fourth row — second component</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/client/public/templates/PriceRight_Intermediates_Import_Template.xlsx
+++ b/client/public/templates/PriceRight_Intermediates_Import_Template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A66"/>
   <cols>
     <col min="1" max="1" width="100.83203125" customWidth="1"/>
   </cols>
@@ -720,49 +720,29 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v xml:space="preserve">  Notes — Optional</v>
+        <v>SAMPLE DATA:</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v xml:space="preserve">    Any additional notes</v>
+        <v>The Import Data sheet contains sample rows showing the correct format.</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v xml:space="preserve">    Example: Yield-based processing</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>SAMPLE DATA:</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>The Import Data sheet contains sample rows showing the correct format.</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
         <v>Delete them before importing.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A70"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A66"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:I5"/>
   <cols>
     <col min="1" max="1" width="21.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -773,7 +753,6 @@
     <col min="7" max="7" width="18.83203125" customWidth="1"/>
     <col min="8" max="8" width="18.83203125" customWidth="1"/>
     <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,9 +783,6 @@
       <c r="I1" t="str">
         <v>Component Quantity</v>
       </c>
-      <c r="J1" t="str">
-        <v>Notes</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -836,9 +812,6 @@
       <c r="I2">
         <v>25</v>
       </c>
-      <c r="J2" t="str">
-        <v>First component — main ingredient</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -868,9 +841,6 @@
       <c r="I3">
         <v>0.5</v>
       </c>
-      <c r="J3" t="str">
-        <v>Second component — same intermediate</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -900,9 +870,6 @@
       <c r="I4">
         <v>7</v>
       </c>
-      <c r="J4" t="str">
-        <v>Third row — different intermediate</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -932,13 +899,10 @@
       <c r="I5">
         <v>1.5</v>
       </c>
-      <c r="J5" t="str">
-        <v>Fourth row — second component</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I5"/>
   </ignoredErrors>
 </worksheet>
 </file>